--- a/p6_deployment/data/usa/missing/data_understanding/all/df_match_player_miss.xlsx
+++ b/p6_deployment/data/usa/missing/data_understanding/all/df_match_player_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GE108"/>
+  <dimension ref="A1:GE110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78435,6 +78435,1368 @@
       <c r="GD108" t="inlineStr"/>
       <c r="GE108" t="inlineStr"/>
     </row>
+    <row r="109">
+      <c r="A109" s="1" t="inlineStr">
+        <is>
+          <t>COgk2UVd</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>I5BDsX50</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>lee jackson</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>r5zgq7ga</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>twumasi kofi</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>SdGJHbfQ</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>yao karifa</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>fZOV3MQb</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>nodarse frank</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>pMiZqUWF</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>turnbull stephen</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>ABgybAKc</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>holstad clay</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>fFGWyWGc</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>brito joe</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>GUL6UkS5</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>ybarra marc</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>bPFJK7Aq</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>kwizera jojea</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>djBFSyEl</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>dikwa albert</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>CzZq1qid</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>williams jj</t>
+        </is>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>dOxI9MKG</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>pasquel ramon</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>2JN1MDYl</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>lyons miles</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>bmja4NbJ</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>craig brandan</t>
+        </is>
+      </c>
+      <c r="AD109" t="inlineStr">
+        <is>
+          <t>61u8Ap9R</t>
+        </is>
+      </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>dollenmayer noah</t>
+        </is>
+      </c>
+      <c r="AF109" t="inlineStr">
+        <is>
+          <t>pY0wQDfp</t>
+        </is>
+      </c>
+      <c r="AG109" t="inlineStr">
+        <is>
+          <t>borelli eder</t>
+        </is>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>2aWqq3yE</t>
+        </is>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>calvillo eric</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>2Lu27gga</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>akinyode bolu</t>
+        </is>
+      </c>
+      <c r="AL109" t="inlineStr">
+        <is>
+          <t>GYF2Siak</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>zacarias ricardo</t>
+        </is>
+      </c>
+      <c r="AN109" t="inlineStr">
+        <is>
+          <t>IVAH3POn</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>nevarez francisco</t>
+        </is>
+      </c>
+      <c r="AP109" t="inlineStr">
+        <is>
+          <t>40hYTKFF</t>
+        </is>
+      </c>
+      <c r="AQ109" t="inlineStr">
+        <is>
+          <t>moshobane tumi</t>
+        </is>
+      </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>61YPh7Nh</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr">
+        <is>
+          <t>garay jeremy</t>
+        </is>
+      </c>
+      <c r="AT109" t="inlineStr">
+        <is>
+          <t>QLwBlkVS</t>
+        </is>
+      </c>
+      <c r="AU109" t="inlineStr">
+        <is>
+          <t>angking isaac</t>
+        </is>
+      </c>
+      <c r="AV109" t="inlineStr">
+        <is>
+          <t>pCy6heIQ</t>
+        </is>
+      </c>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>doyle mark</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>vaN7FIP6</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t>fuson noah</t>
+        </is>
+      </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>YguzBHPo</t>
+        </is>
+      </c>
+      <c r="BA109" t="inlineStr">
+        <is>
+          <t>koke vegas</t>
+        </is>
+      </c>
+      <c r="BB109" t="inlineStr">
+        <is>
+          <t>SKDsui3p</t>
+        </is>
+      </c>
+      <c r="BC109" t="inlineStr">
+        <is>
+          <t>mcglynn conor</t>
+        </is>
+      </c>
+      <c r="BD109" t="inlineStr">
+        <is>
+          <t>p4My3U8s</t>
+        </is>
+      </c>
+      <c r="BE109" t="inlineStr">
+        <is>
+          <t>orduy kevin</t>
+        </is>
+      </c>
+      <c r="BF109" t="inlineStr">
+        <is>
+          <t>Auz4PTZ3</t>
+        </is>
+      </c>
+      <c r="BG109" t="inlineStr">
+        <is>
+          <t>smith collin</t>
+        </is>
+      </c>
+      <c r="BH109" t="inlineStr">
+        <is>
+          <t>S4F7Co96</t>
+        </is>
+      </c>
+      <c r="BI109" t="inlineStr">
+        <is>
+          <t>vang kevin</t>
+        </is>
+      </c>
+      <c r="BJ109" t="inlineStr">
+        <is>
+          <t>lCUVNwwn</t>
+        </is>
+      </c>
+      <c r="BK109" t="inlineStr">
+        <is>
+          <t>dhillon justin</t>
+        </is>
+      </c>
+      <c r="BL109" t="inlineStr">
+        <is>
+          <t>OKIXsIIl</t>
+        </is>
+      </c>
+      <c r="BM109" t="inlineStr">
+        <is>
+          <t>garcia javier</t>
+        </is>
+      </c>
+      <c r="BN109" t="inlineStr">
+        <is>
+          <t>Ummi57wm</t>
+        </is>
+      </c>
+      <c r="BO109" t="inlineStr">
+        <is>
+          <t>hinds nick</t>
+        </is>
+      </c>
+      <c r="BP109" t="inlineStr">
+        <is>
+          <t>pASl4ZnA</t>
+        </is>
+      </c>
+      <c r="BQ109" t="inlineStr">
+        <is>
+          <t>moreno amando</t>
+        </is>
+      </c>
+      <c r="BR109" t="inlineStr">
+        <is>
+          <t>vR4farZA</t>
+        </is>
+      </c>
+      <c r="BS109" t="inlineStr">
+        <is>
+          <t>petrovic petar</t>
+        </is>
+      </c>
+      <c r="BT109" t="inlineStr">
+        <is>
+          <t>Kfa88uP3</t>
+        </is>
+      </c>
+      <c r="BU109" t="inlineStr">
+        <is>
+          <t>rivas joaquin</t>
+        </is>
+      </c>
+      <c r="BV109" t="inlineStr">
+        <is>
+          <t>nuON8BH2</t>
+        </is>
+      </c>
+      <c r="BW109" t="inlineStr">
+        <is>
+          <t>yuma</t>
+        </is>
+      </c>
+      <c r="BX109" t="inlineStr"/>
+      <c r="BY109" t="inlineStr"/>
+      <c r="BZ109" t="inlineStr"/>
+      <c r="CA109" t="inlineStr"/>
+      <c r="CB109" t="inlineStr">
+        <is>
+          <t>SKDsui3p</t>
+        </is>
+      </c>
+      <c r="CC109" t="inlineStr">
+        <is>
+          <t>mcglynn conor</t>
+        </is>
+      </c>
+      <c r="CD109" t="inlineStr">
+        <is>
+          <t>SKDsui3p</t>
+        </is>
+      </c>
+      <c r="CE109" t="inlineStr">
+        <is>
+          <t>mcglynn conor</t>
+        </is>
+      </c>
+      <c r="CF109" t="inlineStr">
+        <is>
+          <t>r5zgq7ga</t>
+        </is>
+      </c>
+      <c r="CG109" t="inlineStr">
+        <is>
+          <t>twumasi kofi</t>
+        </is>
+      </c>
+      <c r="CH109" t="inlineStr">
+        <is>
+          <t>QLwBlkVS</t>
+        </is>
+      </c>
+      <c r="CI109" t="inlineStr">
+        <is>
+          <t>angking isaac</t>
+        </is>
+      </c>
+      <c r="CJ109" t="inlineStr">
+        <is>
+          <t>QLwBlkVS</t>
+        </is>
+      </c>
+      <c r="CK109" t="inlineStr">
+        <is>
+          <t>angking isaac</t>
+        </is>
+      </c>
+      <c r="CL109" t="inlineStr">
+        <is>
+          <t>fFGWyWGc</t>
+        </is>
+      </c>
+      <c r="CM109" t="inlineStr">
+        <is>
+          <t>brito joe</t>
+        </is>
+      </c>
+      <c r="CN109" t="inlineStr">
+        <is>
+          <t>Auz4PTZ3</t>
+        </is>
+      </c>
+      <c r="CO109" t="inlineStr">
+        <is>
+          <t>smith collin</t>
+        </is>
+      </c>
+      <c r="CP109" t="inlineStr">
+        <is>
+          <t>Auz4PTZ3</t>
+        </is>
+      </c>
+      <c r="CQ109" t="inlineStr">
+        <is>
+          <t>smith collin</t>
+        </is>
+      </c>
+      <c r="CR109" t="inlineStr">
+        <is>
+          <t>pMiZqUWF</t>
+        </is>
+      </c>
+      <c r="CS109" t="inlineStr">
+        <is>
+          <t>turnbull stephen</t>
+        </is>
+      </c>
+      <c r="CT109" t="inlineStr">
+        <is>
+          <t>vaN7FIP6</t>
+        </is>
+      </c>
+      <c r="CU109" t="inlineStr">
+        <is>
+          <t>fuson noah</t>
+        </is>
+      </c>
+      <c r="CV109" t="inlineStr">
+        <is>
+          <t>vaN7FIP6</t>
+        </is>
+      </c>
+      <c r="CW109" t="inlineStr">
+        <is>
+          <t>fuson noah</t>
+        </is>
+      </c>
+      <c r="CX109" t="inlineStr">
+        <is>
+          <t>bPFJK7Aq</t>
+        </is>
+      </c>
+      <c r="CY109" t="inlineStr">
+        <is>
+          <t>kwizera jojea</t>
+        </is>
+      </c>
+      <c r="CZ109" t="inlineStr"/>
+      <c r="DA109" t="inlineStr"/>
+      <c r="DB109" t="inlineStr"/>
+      <c r="DC109" t="inlineStr"/>
+      <c r="DD109" t="inlineStr"/>
+      <c r="DE109" t="inlineStr"/>
+      <c r="DF109" t="inlineStr">
+        <is>
+          <t>pASl4ZnA</t>
+        </is>
+      </c>
+      <c r="DG109" t="inlineStr">
+        <is>
+          <t>moreno amando</t>
+        </is>
+      </c>
+      <c r="DH109" t="inlineStr">
+        <is>
+          <t>pASl4ZnA</t>
+        </is>
+      </c>
+      <c r="DI109" t="inlineStr">
+        <is>
+          <t>moreno amando</t>
+        </is>
+      </c>
+      <c r="DJ109" t="inlineStr">
+        <is>
+          <t>61YPh7Nh</t>
+        </is>
+      </c>
+      <c r="DK109" t="inlineStr">
+        <is>
+          <t>garay jeremy</t>
+        </is>
+      </c>
+      <c r="DL109" t="inlineStr">
+        <is>
+          <t>lCUVNwwn</t>
+        </is>
+      </c>
+      <c r="DM109" t="inlineStr">
+        <is>
+          <t>dhillon justin</t>
+        </is>
+      </c>
+      <c r="DN109" t="inlineStr">
+        <is>
+          <t>lCUVNwwn</t>
+        </is>
+      </c>
+      <c r="DO109" t="inlineStr">
+        <is>
+          <t>dhillon justin</t>
+        </is>
+      </c>
+      <c r="DP109" t="inlineStr">
+        <is>
+          <t>GYF2Siak</t>
+        </is>
+      </c>
+      <c r="DQ109" t="inlineStr">
+        <is>
+          <t>zacarias ricardo</t>
+        </is>
+      </c>
+      <c r="DR109" t="inlineStr">
+        <is>
+          <t>vR4farZA</t>
+        </is>
+      </c>
+      <c r="DS109" t="inlineStr">
+        <is>
+          <t>petrovic petar</t>
+        </is>
+      </c>
+      <c r="DT109" t="inlineStr">
+        <is>
+          <t>vR4farZA</t>
+        </is>
+      </c>
+      <c r="DU109" t="inlineStr">
+        <is>
+          <t>petrovic petar</t>
+        </is>
+      </c>
+      <c r="DV109" t="inlineStr">
+        <is>
+          <t>2Lu27gga</t>
+        </is>
+      </c>
+      <c r="DW109" t="inlineStr">
+        <is>
+          <t>akinyode bolu</t>
+        </is>
+      </c>
+      <c r="DX109" t="inlineStr">
+        <is>
+          <t>Kfa88uP3</t>
+        </is>
+      </c>
+      <c r="DY109" t="inlineStr">
+        <is>
+          <t>rivas joaquin</t>
+        </is>
+      </c>
+      <c r="DZ109" t="inlineStr">
+        <is>
+          <t>Kfa88uP3</t>
+        </is>
+      </c>
+      <c r="EA109" t="inlineStr">
+        <is>
+          <t>rivas joaquin</t>
+        </is>
+      </c>
+      <c r="EB109" t="inlineStr">
+        <is>
+          <t>40hYTKFF</t>
+        </is>
+      </c>
+      <c r="EC109" t="inlineStr">
+        <is>
+          <t>moshobane tumi</t>
+        </is>
+      </c>
+      <c r="ED109" t="inlineStr">
+        <is>
+          <t>Ummi57wm</t>
+        </is>
+      </c>
+      <c r="EE109" t="inlineStr">
+        <is>
+          <t>hinds nick</t>
+        </is>
+      </c>
+      <c r="EF109" t="inlineStr">
+        <is>
+          <t>Ummi57wm</t>
+        </is>
+      </c>
+      <c r="EG109" t="inlineStr">
+        <is>
+          <t>hinds nick</t>
+        </is>
+      </c>
+      <c r="EH109" t="inlineStr">
+        <is>
+          <t>pY0wQDfp</t>
+        </is>
+      </c>
+      <c r="EI109" t="inlineStr">
+        <is>
+          <t>borelli eder</t>
+        </is>
+      </c>
+      <c r="EJ109" t="inlineStr"/>
+      <c r="EK109" t="inlineStr"/>
+      <c r="EL109" t="inlineStr"/>
+      <c r="EM109" t="inlineStr"/>
+      <c r="EN109" t="inlineStr"/>
+      <c r="EO109" t="inlineStr"/>
+      <c r="EP109" t="inlineStr"/>
+      <c r="EQ109" t="inlineStr"/>
+      <c r="ER109" t="inlineStr"/>
+      <c r="ES109" t="inlineStr"/>
+      <c r="ET109" t="inlineStr"/>
+      <c r="EU109" t="inlineStr"/>
+      <c r="EV109" t="inlineStr"/>
+      <c r="EW109" t="inlineStr"/>
+      <c r="EX109" t="inlineStr"/>
+      <c r="EY109" t="inlineStr"/>
+      <c r="EZ109" t="inlineStr"/>
+      <c r="FA109" t="inlineStr"/>
+      <c r="FB109" t="inlineStr"/>
+      <c r="FC109" t="inlineStr"/>
+      <c r="FD109" t="inlineStr"/>
+      <c r="FE109" t="inlineStr"/>
+      <c r="FF109" t="inlineStr"/>
+      <c r="FG109" t="inlineStr"/>
+      <c r="FH109" t="inlineStr"/>
+      <c r="FI109" t="inlineStr"/>
+      <c r="FJ109" t="inlineStr"/>
+      <c r="FK109" t="inlineStr"/>
+      <c r="FL109" t="inlineStr"/>
+      <c r="FM109" t="inlineStr"/>
+      <c r="FN109" t="inlineStr"/>
+      <c r="FO109" t="inlineStr"/>
+      <c r="FP109" t="inlineStr"/>
+      <c r="FQ109" t="inlineStr"/>
+      <c r="FR109" t="inlineStr"/>
+      <c r="FS109" t="inlineStr"/>
+      <c r="FT109" t="inlineStr"/>
+      <c r="FU109" t="inlineStr"/>
+      <c r="FV109" t="inlineStr"/>
+      <c r="FW109" t="inlineStr"/>
+      <c r="FX109" t="inlineStr"/>
+      <c r="FY109" t="inlineStr"/>
+      <c r="FZ109" t="inlineStr"/>
+      <c r="GA109" t="inlineStr"/>
+      <c r="GB109" t="inlineStr"/>
+      <c r="GC109" t="inlineStr"/>
+      <c r="GD109" t="inlineStr"/>
+      <c r="GE109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="inlineStr">
+        <is>
+          <t>bL57wogd</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>67li1ynd</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>saldana carlos</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>AitxpHkS</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>sheldon matthew</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>4zLmP9V3</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>carroll stephen</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>lErgyewE</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>amoo mensah devon</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Gz4oOThB</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>levis brett</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>IRtMcckd</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>williams rhys</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>hrfUopwP</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>murphy james</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>vVJtIvTu</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>abdoulaye diop</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>td2rqnzC</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>morris ben</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>zRXV8mvM</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>rodriguez maxi</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>C46Ufw7d</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>amoh elvis</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>YVRXszaF</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>hibbert jayden</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>O8S4A8iq</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>dodson derek</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>WjEIUyMQ</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>crognale alex</t>
+        </is>
+      </c>
+      <c r="AD110" t="inlineStr">
+        <is>
+          <t>hv6lPAU9</t>
+        </is>
+      </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>kavita phanuel</t>
+        </is>
+      </c>
+      <c r="AF110" t="inlineStr">
+        <is>
+          <t>2ZC96wer</t>
+        </is>
+      </c>
+      <c r="AG110" t="inlineStr">
+        <is>
+          <t>paterson aj</t>
+        </is>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>noFkUkB1</t>
+        </is>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>tabortetaka preston</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>Emuusx6F</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>hernandez foster kobe</t>
+        </is>
+      </c>
+      <c r="AL110" t="inlineStr">
+        <is>
+          <t>W0IPa6za</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>perez miguel</t>
+        </is>
+      </c>
+      <c r="AN110" t="inlineStr">
+        <is>
+          <t>hhqa8nNc</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>kassim prosper</t>
+        </is>
+      </c>
+      <c r="AP110" t="inlineStr">
+        <is>
+          <t>OYA19zBf</t>
+        </is>
+      </c>
+      <c r="AQ110" t="inlineStr">
+        <is>
+          <t>martinez enzo</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>6Dhlor2O</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr">
+        <is>
+          <t>pasher tyler</t>
+        </is>
+      </c>
+      <c r="AT110" t="inlineStr">
+        <is>
+          <t>ATW1gdHm</t>
+        </is>
+      </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>bezerra victor</t>
+        </is>
+      </c>
+      <c r="AV110" t="inlineStr">
+        <is>
+          <t>Cn8rU1bf</t>
+        </is>
+      </c>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>gasso dominic</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>2XXjV3ia</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t>matthews yazeed</t>
+        </is>
+      </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>ENKoHGRC</t>
+        </is>
+      </c>
+      <c r="BA110" t="inlineStr">
+        <is>
+          <t>salim abdi</t>
+        </is>
+      </c>
+      <c r="BB110" t="inlineStr">
+        <is>
+          <t>vs4ZkyjL</t>
+        </is>
+      </c>
+      <c r="BC110" t="inlineStr">
+        <is>
+          <t>steinwascher nathan</t>
+        </is>
+      </c>
+      <c r="BD110" t="inlineStr">
+        <is>
+          <t>GQtRHQGM</t>
+        </is>
+      </c>
+      <c r="BE110" t="inlineStr">
+        <is>
+          <t>villanueva alex</t>
+        </is>
+      </c>
+      <c r="BF110" t="inlineStr">
+        <is>
+          <t>847Q5dgk</t>
+        </is>
+      </c>
+      <c r="BG110" t="inlineStr">
+        <is>
+          <t>williams ryan</t>
+        </is>
+      </c>
+      <c r="BH110" t="inlineStr"/>
+      <c r="BI110" t="inlineStr"/>
+      <c r="BJ110" t="inlineStr">
+        <is>
+          <t>dbxK7ytt</t>
+        </is>
+      </c>
+      <c r="BK110" t="inlineStr">
+        <is>
+          <t>calloway finn</t>
+        </is>
+      </c>
+      <c r="BL110" t="inlineStr">
+        <is>
+          <t>vZe9Zyx8</t>
+        </is>
+      </c>
+      <c r="BM110" t="inlineStr">
+        <is>
+          <t>hamouda ramiz</t>
+        </is>
+      </c>
+      <c r="BN110" t="inlineStr">
+        <is>
+          <t>fgUneYj4</t>
+        </is>
+      </c>
+      <c r="BO110" t="inlineStr">
+        <is>
+          <t>jack owen</t>
+        </is>
+      </c>
+      <c r="BP110" t="inlineStr">
+        <is>
+          <t>2sG4esMB</t>
+        </is>
+      </c>
+      <c r="BQ110" t="inlineStr">
+        <is>
+          <t>mensah moses</t>
+        </is>
+      </c>
+      <c r="BR110" t="inlineStr">
+        <is>
+          <t>fymCnmrE</t>
+        </is>
+      </c>
+      <c r="BS110" t="inlineStr">
+        <is>
+          <t>nwegbo diba</t>
+        </is>
+      </c>
+      <c r="BT110" t="inlineStr"/>
+      <c r="BU110" t="inlineStr"/>
+      <c r="BV110" t="inlineStr"/>
+      <c r="BW110" t="inlineStr"/>
+      <c r="BX110" t="inlineStr"/>
+      <c r="BY110" t="inlineStr"/>
+      <c r="BZ110" t="inlineStr"/>
+      <c r="CA110" t="inlineStr"/>
+      <c r="CB110" t="inlineStr">
+        <is>
+          <t>GQtRHQGM</t>
+        </is>
+      </c>
+      <c r="CC110" t="inlineStr">
+        <is>
+          <t>villanueva alex</t>
+        </is>
+      </c>
+      <c r="CD110" t="inlineStr">
+        <is>
+          <t>GQtRHQGM</t>
+        </is>
+      </c>
+      <c r="CE110" t="inlineStr">
+        <is>
+          <t>villanueva alex</t>
+        </is>
+      </c>
+      <c r="CF110" t="inlineStr">
+        <is>
+          <t>Gz4oOThB</t>
+        </is>
+      </c>
+      <c r="CG110" t="inlineStr">
+        <is>
+          <t>levis brett</t>
+        </is>
+      </c>
+      <c r="CH110" t="inlineStr">
+        <is>
+          <t>847Q5dgk</t>
+        </is>
+      </c>
+      <c r="CI110" t="inlineStr">
+        <is>
+          <t>williams ryan</t>
+        </is>
+      </c>
+      <c r="CJ110" t="inlineStr">
+        <is>
+          <t>847Q5dgk</t>
+        </is>
+      </c>
+      <c r="CK110" t="inlineStr">
+        <is>
+          <t>williams ryan</t>
+        </is>
+      </c>
+      <c r="CL110" t="inlineStr">
+        <is>
+          <t>IRtMcckd</t>
+        </is>
+      </c>
+      <c r="CM110" t="inlineStr">
+        <is>
+          <t>williams rhys</t>
+        </is>
+      </c>
+      <c r="CN110" t="inlineStr">
+        <is>
+          <t>2XXjV3ia</t>
+        </is>
+      </c>
+      <c r="CO110" t="inlineStr">
+        <is>
+          <t>matthews yazeed</t>
+        </is>
+      </c>
+      <c r="CP110" t="inlineStr">
+        <is>
+          <t>2XXjV3ia</t>
+        </is>
+      </c>
+      <c r="CQ110" t="inlineStr">
+        <is>
+          <t>matthews yazeed</t>
+        </is>
+      </c>
+      <c r="CR110" t="inlineStr">
+        <is>
+          <t>C46Ufw7d</t>
+        </is>
+      </c>
+      <c r="CS110" t="inlineStr">
+        <is>
+          <t>amoh elvis</t>
+        </is>
+      </c>
+      <c r="CT110" t="inlineStr">
+        <is>
+          <t>ENKoHGRC</t>
+        </is>
+      </c>
+      <c r="CU110" t="inlineStr">
+        <is>
+          <t>salim abdi</t>
+        </is>
+      </c>
+      <c r="CV110" t="inlineStr">
+        <is>
+          <t>ENKoHGRC</t>
+        </is>
+      </c>
+      <c r="CW110" t="inlineStr">
+        <is>
+          <t>salim abdi</t>
+        </is>
+      </c>
+      <c r="CX110" t="inlineStr">
+        <is>
+          <t>GQtRHQGM</t>
+        </is>
+      </c>
+      <c r="CY110" t="inlineStr">
+        <is>
+          <t>villanueva alex</t>
+        </is>
+      </c>
+      <c r="CZ110" t="inlineStr">
+        <is>
+          <t>Cn8rU1bf</t>
+        </is>
+      </c>
+      <c r="DA110" t="inlineStr">
+        <is>
+          <t>gasso dominic</t>
+        </is>
+      </c>
+      <c r="DB110" t="inlineStr">
+        <is>
+          <t>Cn8rU1bf</t>
+        </is>
+      </c>
+      <c r="DC110" t="inlineStr">
+        <is>
+          <t>gasso dominic</t>
+        </is>
+      </c>
+      <c r="DD110" t="inlineStr">
+        <is>
+          <t>hrfUopwP</t>
+        </is>
+      </c>
+      <c r="DE110" t="inlineStr">
+        <is>
+          <t>murphy james</t>
+        </is>
+      </c>
+      <c r="DF110" t="inlineStr">
+        <is>
+          <t>2sG4esMB</t>
+        </is>
+      </c>
+      <c r="DG110" t="inlineStr">
+        <is>
+          <t>mensah moses</t>
+        </is>
+      </c>
+      <c r="DH110" t="inlineStr">
+        <is>
+          <t>2sG4esMB</t>
+        </is>
+      </c>
+      <c r="DI110" t="inlineStr">
+        <is>
+          <t>mensah moses</t>
+        </is>
+      </c>
+      <c r="DJ110" t="inlineStr">
+        <is>
+          <t>W0IPa6za</t>
+        </is>
+      </c>
+      <c r="DK110" t="inlineStr">
+        <is>
+          <t>perez miguel</t>
+        </is>
+      </c>
+      <c r="DL110" t="inlineStr">
+        <is>
+          <t>fymCnmrE</t>
+        </is>
+      </c>
+      <c r="DM110" t="inlineStr">
+        <is>
+          <t>nwegbo diba</t>
+        </is>
+      </c>
+      <c r="DN110" t="inlineStr">
+        <is>
+          <t>fymCnmrE</t>
+        </is>
+      </c>
+      <c r="DO110" t="inlineStr">
+        <is>
+          <t>nwegbo diba</t>
+        </is>
+      </c>
+      <c r="DP110" t="inlineStr">
+        <is>
+          <t>hhqa8nNc</t>
+        </is>
+      </c>
+      <c r="DQ110" t="inlineStr">
+        <is>
+          <t>kassim prosper</t>
+        </is>
+      </c>
+      <c r="DR110" t="inlineStr">
+        <is>
+          <t>vZe9Zyx8</t>
+        </is>
+      </c>
+      <c r="DS110" t="inlineStr">
+        <is>
+          <t>hamouda ramiz</t>
+        </is>
+      </c>
+      <c r="DT110" t="inlineStr">
+        <is>
+          <t>vZe9Zyx8</t>
+        </is>
+      </c>
+      <c r="DU110" t="inlineStr">
+        <is>
+          <t>hamouda ramiz</t>
+        </is>
+      </c>
+      <c r="DV110" t="inlineStr">
+        <is>
+          <t>noFkUkB1</t>
+        </is>
+      </c>
+      <c r="DW110" t="inlineStr">
+        <is>
+          <t>tabortetaka preston</t>
+        </is>
+      </c>
+      <c r="DX110" t="inlineStr"/>
+      <c r="DY110" t="inlineStr"/>
+      <c r="DZ110" t="inlineStr"/>
+      <c r="EA110" t="inlineStr"/>
+      <c r="EB110" t="inlineStr"/>
+      <c r="EC110" t="inlineStr"/>
+      <c r="ED110" t="inlineStr"/>
+      <c r="EE110" t="inlineStr"/>
+      <c r="EF110" t="inlineStr"/>
+      <c r="EG110" t="inlineStr"/>
+      <c r="EH110" t="inlineStr"/>
+      <c r="EI110" t="inlineStr"/>
+      <c r="EJ110" t="inlineStr"/>
+      <c r="EK110" t="inlineStr"/>
+      <c r="EL110" t="inlineStr"/>
+      <c r="EM110" t="inlineStr"/>
+      <c r="EN110" t="inlineStr"/>
+      <c r="EO110" t="inlineStr"/>
+      <c r="EP110" t="inlineStr"/>
+      <c r="EQ110" t="inlineStr"/>
+      <c r="ER110" t="inlineStr"/>
+      <c r="ES110" t="inlineStr"/>
+      <c r="ET110" t="inlineStr"/>
+      <c r="EU110" t="inlineStr"/>
+      <c r="EV110" t="inlineStr"/>
+      <c r="EW110" t="inlineStr"/>
+      <c r="EX110" t="inlineStr"/>
+      <c r="EY110" t="inlineStr"/>
+      <c r="EZ110" t="inlineStr"/>
+      <c r="FA110" t="inlineStr"/>
+      <c r="FB110" t="inlineStr"/>
+      <c r="FC110" t="inlineStr"/>
+      <c r="FD110" t="inlineStr"/>
+      <c r="FE110" t="inlineStr"/>
+      <c r="FF110" t="inlineStr"/>
+      <c r="FG110" t="inlineStr"/>
+      <c r="FH110" t="inlineStr"/>
+      <c r="FI110" t="inlineStr"/>
+      <c r="FJ110" t="inlineStr"/>
+      <c r="FK110" t="inlineStr"/>
+      <c r="FL110" t="inlineStr"/>
+      <c r="FM110" t="inlineStr"/>
+      <c r="FN110" t="inlineStr"/>
+      <c r="FO110" t="inlineStr"/>
+      <c r="FP110" t="inlineStr"/>
+      <c r="FQ110" t="inlineStr"/>
+      <c r="FR110" t="inlineStr"/>
+      <c r="FS110" t="inlineStr"/>
+      <c r="FT110" t="inlineStr"/>
+      <c r="FU110" t="inlineStr"/>
+      <c r="FV110" t="inlineStr"/>
+      <c r="FW110" t="inlineStr"/>
+      <c r="FX110" t="inlineStr"/>
+      <c r="FY110" t="inlineStr"/>
+      <c r="FZ110" t="inlineStr"/>
+      <c r="GA110" t="inlineStr"/>
+      <c r="GB110" t="inlineStr"/>
+      <c r="GC110" t="inlineStr"/>
+      <c r="GD110" t="inlineStr"/>
+      <c r="GE110" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
